--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,6 +1197,112 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129529378</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97595</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skammelstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573926</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6296100</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129459535</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129466053</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129459535</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129466053</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129459535</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>129466053</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129465089</v>
       </c>
       <c r="B2" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129464954</v>
       </c>
       <c r="B5" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129465013</v>
       </c>
       <c r="B6" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52065-2025 artfynd.xlsx
+++ b/artfynd/A 52065-2025 artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>129529378</v>
       </c>
       <c r="B7" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
